--- a/data/dividends_info_20260818.xlsx
+++ b/data/dividends_info_20260818.xlsx
@@ -523,10 +523,10 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>47.54000091552734</v>
+        <v>45.31000137329102</v>
       </c>
       <c r="I2" t="n">
-        <v>0.1893142580285574</v>
+        <v>0.1986316426224001</v>
       </c>
       <c r="J2" t="n">
         <v>209</v>
@@ -570,10 +570,10 @@
         </is>
       </c>
       <c r="H3" t="n">
-        <v>66.5</v>
+        <v>66.25</v>
       </c>
       <c r="I3" t="n">
-        <v>1.052631578947368</v>
+        <v>1.056603773584906</v>
       </c>
       <c r="J3" t="n">
         <v>188</v>
@@ -617,10 +617,10 @@
         </is>
       </c>
       <c r="H4" t="n">
-        <v>9.300000190734863</v>
+        <v>9.159999847412109</v>
       </c>
       <c r="I4" t="n">
-        <v>0.6451612770908873</v>
+        <v>0.6550218449725329</v>
       </c>
       <c r="J4" t="n">
         <v>118</v>
@@ -663,12 +663,8 @@
           <t>IT0004587470</t>
         </is>
       </c>
-      <c r="H5" t="n">
-        <v>0.4659999907016754</v>
-      </c>
-      <c r="I5" t="n">
-        <v>0.8583691158399027</v>
-      </c>
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr"/>
       <c r="J5" t="n">
         <v>118</v>
       </c>
@@ -711,10 +707,10 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>47.54000091552734</v>
+        <v>45.31000137329102</v>
       </c>
       <c r="I6" t="n">
-        <v>0.1893142580285574</v>
+        <v>0.1986316426224001</v>
       </c>
       <c r="J6" t="n">
         <v>118</v>
@@ -758,10 +754,10 @@
         </is>
       </c>
       <c r="H7" t="n">
-        <v>2.109999895095825</v>
+        <v>2.099999904632568</v>
       </c>
       <c r="I7" t="n">
-        <v>3.649289280960038</v>
+        <v>3.666666833181238</v>
       </c>
       <c r="J7" t="n">
         <v>97</v>
@@ -805,10 +801,10 @@
         </is>
       </c>
       <c r="H8" t="n">
-        <v>23.96999931335449</v>
+        <v>24</v>
       </c>
       <c r="I8" t="n">
-        <v>1.126408042279642</v>
+        <v>1.125</v>
       </c>
       <c r="J8" t="n">
         <v>97</v>
@@ -852,10 +848,10 @@
         </is>
       </c>
       <c r="H9" t="n">
-        <v>23.01000022888184</v>
+        <v>22.8799991607666</v>
       </c>
       <c r="I9" t="n">
-        <v>2.564102538597284</v>
+        <v>2.578671423256433</v>
       </c>
       <c r="J9" t="n">
         <v>97</v>
@@ -899,10 +895,10 @@
         </is>
       </c>
       <c r="H10" t="n">
-        <v>5.809999942779541</v>
+        <v>5.769999980926514</v>
       </c>
       <c r="I10" t="n">
-        <v>3.442340825640675</v>
+        <v>3.466204517523849</v>
       </c>
       <c r="J10" t="n">
         <v>90</v>
@@ -946,10 +942,10 @@
         </is>
       </c>
       <c r="H11" t="n">
-        <v>10.26000022888184</v>
+        <v>10.10999965667725</v>
       </c>
       <c r="I11" t="n">
-        <v>4.483430699203134</v>
+        <v>4.549950698526371</v>
       </c>
       <c r="J11" t="n">
         <v>69</v>
@@ -993,10 +989,10 @@
         </is>
       </c>
       <c r="H12" t="n">
-        <v>7.449999809265137</v>
+        <v>7.550000190734863</v>
       </c>
       <c r="I12" t="n">
-        <v>0.8053691481358354</v>
+        <v>0.7947019666784939</v>
       </c>
       <c r="J12" t="n">
         <v>62</v>
@@ -1039,12 +1035,8 @@
           <t>IT0004587470</t>
         </is>
       </c>
-      <c r="H13" t="n">
-        <v>0.4979999959468842</v>
-      </c>
-      <c r="I13" t="n">
-        <v>0.8032128579428007</v>
-      </c>
+      <c r="H13" t="inlineStr"/>
+      <c r="I13" t="inlineStr"/>
       <c r="J13" t="n">
         <v>62</v>
       </c>
@@ -1134,10 +1126,10 @@
         </is>
       </c>
       <c r="H15" t="n">
-        <v>5.079999923706055</v>
+        <v>4.960000038146973</v>
       </c>
       <c r="I15" t="n">
-        <v>0.7480315072972982</v>
+        <v>0.7661290263658259</v>
       </c>
       <c r="J15" t="n">
         <v>41</v>
@@ -1181,10 +1173,10 @@
         </is>
       </c>
       <c r="H16" t="n">
-        <v>23.96999931335449</v>
+        <v>24</v>
       </c>
       <c r="I16" t="n">
-        <v>1.126408042279642</v>
+        <v>1.125</v>
       </c>
       <c r="J16" t="n">
         <v>34</v>
@@ -1228,10 +1220,10 @@
         </is>
       </c>
       <c r="H17" t="n">
-        <v>1.952000021934509</v>
+        <v>1.963000059127808</v>
       </c>
       <c r="I17" t="n">
-        <v>2.920081934400326</v>
+        <v>2.903718710295201</v>
       </c>
       <c r="J17" t="n">
         <v>34</v>
@@ -1275,10 +1267,10 @@
         </is>
       </c>
       <c r="H18" t="n">
-        <v>47.54000091552734</v>
+        <v>45.31000137329102</v>
       </c>
       <c r="I18" t="n">
-        <v>0.1893142580285574</v>
+        <v>0.1986316426224001</v>
       </c>
       <c r="J18" t="n">
         <v>34</v>
@@ -1322,10 +1314,10 @@
         </is>
       </c>
       <c r="H19" t="n">
-        <v>92.05000305175781</v>
+        <v>92.19999694824219</v>
       </c>
       <c r="I19" t="n">
-        <v>1.444866872250041</v>
+        <v>1.442516316726794</v>
       </c>
       <c r="J19" t="n">
         <v>34</v>
@@ -1369,10 +1361,10 @@
         </is>
       </c>
       <c r="H20" t="n">
-        <v>5.739999771118164</v>
+        <v>5.860000133514404</v>
       </c>
       <c r="I20" t="n">
-        <v>5.226481044642261</v>
+        <v>5.119453808272897</v>
       </c>
       <c r="J20" t="n">
         <v>27</v>
@@ -1415,12 +1407,8 @@
           <t>IT0004587470</t>
         </is>
       </c>
-      <c r="H21" t="n">
-        <v>0.4979999959468842</v>
-      </c>
-      <c r="I21" t="n">
-        <v>0.8032128579428007</v>
-      </c>
+      <c r="H21" t="inlineStr"/>
+      <c r="I21" t="inlineStr"/>
       <c r="J21" t="n">
         <v>6</v>
       </c>
@@ -1463,10 +1451,10 @@
         </is>
       </c>
       <c r="H22" t="n">
-        <v>2.400000095367432</v>
+        <v>2.480000019073486</v>
       </c>
       <c r="I22" t="n">
-        <v>9.166666302416074</v>
+        <v>8.870967673709565</v>
       </c>
       <c r="J22" t="n">
         <v>-8</v>
@@ -1510,10 +1498,10 @@
         </is>
       </c>
       <c r="H23" t="n">
-        <v>5.079999923706055</v>
+        <v>4.960000038146973</v>
       </c>
       <c r="I23" t="n">
-        <v>0.7480315072972982</v>
+        <v>0.7661290263658259</v>
       </c>
       <c r="J23" t="n">
         <v>-15</v>
@@ -1651,10 +1639,10 @@
         </is>
       </c>
       <c r="H26" t="n">
-        <v>5.96999979019165</v>
+        <v>5.949999809265137</v>
       </c>
       <c r="I26" t="n">
-        <v>4.187604837285504</v>
+        <v>4.201680806959162</v>
       </c>
       <c r="J26" t="n">
         <v>-22</v>
@@ -1698,10 +1686,10 @@
         </is>
       </c>
       <c r="H27" t="n">
-        <v>4.230000019073486</v>
+        <v>4.21999979019165</v>
       </c>
       <c r="I27" t="n">
-        <v>3.30969265647107</v>
+        <v>3.317535709963671</v>
       </c>
       <c r="J27" t="n">
         <v>-29</v>
@@ -1745,10 +1733,10 @@
         </is>
       </c>
       <c r="H28" t="n">
-        <v>9.421999931335449</v>
+        <v>9.482000350952148</v>
       </c>
       <c r="I28" t="n">
-        <v>2.759499064899147</v>
+        <v>2.742037443332216</v>
       </c>
       <c r="J28" t="n">
         <v>-29</v>
@@ -1792,10 +1780,10 @@
         </is>
       </c>
       <c r="H29" t="n">
-        <v>13.60000038146973</v>
+        <v>13.77999973297119</v>
       </c>
       <c r="I29" t="n">
-        <v>4.411764582135689</v>
+        <v>4.354136513982574</v>
       </c>
       <c r="J29" t="n">
         <v>-29</v>
@@ -1839,10 +1827,10 @@
         </is>
       </c>
       <c r="H30" t="n">
-        <v>2.665999889373779</v>
+        <v>2.690000057220459</v>
       </c>
       <c r="I30" t="n">
-        <v>8.252063358175011</v>
+        <v>8.178438487742005</v>
       </c>
       <c r="J30" t="n">
         <v>-29</v>
@@ -1885,12 +1873,8 @@
           <t>IT0004587470</t>
         </is>
       </c>
-      <c r="H31" t="n">
-        <v>0.4979999959468842</v>
-      </c>
-      <c r="I31" t="n">
-        <v>0.8032128579428007</v>
-      </c>
+      <c r="H31" t="inlineStr"/>
+      <c r="I31" t="inlineStr"/>
       <c r="J31" t="n">
         <v>-29</v>
       </c>
@@ -1933,10 +1917,10 @@
         </is>
       </c>
       <c r="H32" t="n">
-        <v>6.614999771118164</v>
+        <v>6.525000095367432</v>
       </c>
       <c r="I32" t="n">
-        <v>3.628118039366639</v>
+        <v>3.67816086578134</v>
       </c>
       <c r="J32" t="n">
         <v>-29</v>
@@ -1980,10 +1964,10 @@
         </is>
       </c>
       <c r="H33" t="n">
-        <v>18.79999923706055</v>
+        <v>18.35000038146973</v>
       </c>
       <c r="I33" t="n">
-        <v>2.000000081163775</v>
+        <v>2.049046278929203</v>
       </c>
       <c r="J33" t="n">
         <v>-29</v>
@@ -3407,78 +3391,9 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C4"/>
+  <dimension ref="A1:A1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Stock</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Date</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Event</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>KME Group S.p.A.</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>2026-09-17</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Half Year Report</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Pattern S.p.A.</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>2026-09-17</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Analyst Presentation</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>RATTI S.p.A. SOCIETA' BENEFIT</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>2026-09-17</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Half Year Report</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
+  <sheetData/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>